--- a/backend/data/financials_by_company/0106.HK.xlsx
+++ b/backend/data/financials_by_company/0106.HK.xlsx
@@ -672,602 +672,602 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-21379003.04699</v>
+        <v>-86072760</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01231</v>
+        <v>0.27</v>
       </c>
       <c r="D2" t="n">
-        <v>391941000</v>
+        <v>124241000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1736719000</v>
+        <v>-318788000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1736719000</v>
+        <v>-318788000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1509333000</v>
+        <v>-777504000</v>
       </c>
       <c r="H2" t="n">
-        <v>20144000</v>
+        <v>62823000</v>
       </c>
       <c r="I2" t="n">
-        <v>1414125000</v>
+        <v>6406403000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1344778000</v>
+        <v>-194547000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1364922000</v>
+        <v>-257370000</v>
       </c>
       <c r="L2" t="n">
-        <v>-119155000</v>
+        <v>-163721000</v>
       </c>
       <c r="M2" t="n">
-        <v>167410000</v>
+        <v>249540000</v>
       </c>
       <c r="N2" t="n">
-        <v>48255000</v>
+        <v>90222000</v>
       </c>
       <c r="O2" t="n">
-        <v>206006996.95301</v>
+        <v>-544788760</v>
       </c>
       <c r="P2" t="n">
-        <v>-1509333000</v>
+        <v>-777504000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1865299000</v>
+        <v>8143990000</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-1826304000</v>
+        <v>-369800000</v>
       </c>
       <c r="T2" t="n">
-        <v>4613371000</v>
+        <v>4590548000</v>
       </c>
       <c r="U2" t="n">
-        <v>4613371000</v>
+        <v>4590548000</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.327</v>
+        <v>-0.169</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.327</v>
+        <v>-0.169</v>
       </c>
       <c r="X2" t="n">
-        <v>-1509333000</v>
+        <v>-777504000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1509333000</v>
+        <v>-777504000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1509333000</v>
+        <v>-777504000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4136000</v>
+        <v>-81313000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1513469000</v>
+        <v>-696191000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1513469000</v>
+        <v>-696191000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-18863000</v>
+        <v>189281000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1532332000</v>
+        <v>-506910000</v>
       </c>
       <c r="AG2" t="n">
-        <v>5430000</v>
+        <v>16626000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1736719000</v>
+        <v>-318788000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1552766000</v>
+        <v>-17543000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>183953000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>275028000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>61303000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>-119155000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>-163721000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>4403000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>167410000</v>
+        <v>249540000</v>
       </c>
       <c r="AO2" t="n">
-        <v>48255000</v>
+        <v>90222000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-139377000</v>
+        <v>-67920000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>451174000</v>
+        <v>1737587000</v>
       </c>
       <c r="AR2" t="n">
-        <v>456184000</v>
+        <v>1768801000</v>
       </c>
       <c r="AS2" t="n">
-        <v>126017000</v>
+        <v>485646000</v>
       </c>
       <c r="AT2" t="n">
-        <v>330167000</v>
+        <v>1283155000</v>
       </c>
       <c r="AU2" t="n">
-        <v>311797000</v>
+        <v>1669667000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1414125000</v>
+        <v>6406403000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1725922000</v>
+        <v>8076070000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1725922000</v>
+        <v>8076070000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-44525880</v>
+        <v>-214453680</v>
       </c>
       <c r="C3" t="n">
         <v>0.21</v>
       </c>
       <c r="D3" t="n">
-        <v>-333516000</v>
+        <v>-266901000</v>
       </c>
       <c r="E3" t="n">
-        <v>-212028000</v>
+        <v>-1021208000</v>
       </c>
       <c r="F3" t="n">
-        <v>-212028000</v>
+        <v>-1021208000</v>
       </c>
       <c r="G3" t="n">
-        <v>-860793000</v>
+        <v>-2588642000</v>
       </c>
       <c r="H3" t="n">
-        <v>81488000</v>
+        <v>75067000</v>
       </c>
       <c r="I3" t="n">
-        <v>7929178000</v>
+        <v>12664689000</v>
       </c>
       <c r="J3" t="n">
-        <v>-545544000</v>
+        <v>-1288109000</v>
       </c>
       <c r="K3" t="n">
-        <v>-627032000</v>
+        <v>-1363176000</v>
       </c>
       <c r="L3" t="n">
-        <v>-199857000</v>
+        <v>-369262000</v>
       </c>
       <c r="M3" t="n">
-        <v>196286000</v>
+        <v>383248000</v>
       </c>
       <c r="N3" t="n">
-        <v>32242000</v>
+        <v>21904000</v>
       </c>
       <c r="O3" t="n">
-        <v>-693290880</v>
+        <v>-1781887680</v>
       </c>
       <c r="P3" t="n">
-        <v>-860793000</v>
+        <v>-2588642000</v>
       </c>
       <c r="Q3" t="n">
-        <v>9443752000</v>
+        <v>14241657000</v>
       </c>
       <c r="R3" t="n">
-        <v>5660000</v>
+        <v>3573000</v>
       </c>
       <c r="S3" t="n">
-        <v>-668420000</v>
+        <v>-1087847000</v>
       </c>
       <c r="T3" t="n">
-        <v>4543175000</v>
+        <v>4545948000</v>
       </c>
       <c r="U3" t="n">
-        <v>4543175000</v>
+        <v>4545948000</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.189</v>
+        <v>-0.569</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.189</v>
+        <v>-0.569</v>
       </c>
       <c r="X3" t="n">
-        <v>-860793000</v>
+        <v>-2588642000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-860793000</v>
+        <v>-2588642000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-860793000</v>
+        <v>-2588642000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2526000</v>
+        <v>-134890000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-863319000</v>
+        <v>-2453752000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-863319000</v>
+        <v>-2453752000</v>
       </c>
       <c r="AE3" t="n">
-        <v>40001000</v>
+        <v>707328000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-823318000</v>
+        <v>-1746424000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6201000</v>
+        <v>-16293000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-212028000</v>
+        <v>-1020925000</v>
       </c>
       <c r="AI3" t="n">
-        <v>17713000</v>
+        <v>209070000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>194315000</v>
+        <v>479215000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>332640000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-199857000</v>
+        <v>-369262000</v>
       </c>
       <c r="AM3" t="n">
-        <v>35813000</v>
+        <v>7918000</v>
       </c>
       <c r="AN3" t="n">
-        <v>196286000</v>
+        <v>383248000</v>
       </c>
       <c r="AO3" t="n">
-        <v>32242000</v>
+        <v>21904000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-403955000</v>
+        <v>-223136000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1514574000</v>
+        <v>1576968000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1520014000</v>
+        <v>1588013000</v>
       </c>
       <c r="AS3" t="n">
-        <v>547287000</v>
+        <v>694776000</v>
       </c>
       <c r="AT3" t="n">
-        <v>972727000</v>
+        <v>893237000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1110619000</v>
+        <v>1353832000</v>
       </c>
       <c r="AV3" t="n">
-        <v>7929178000</v>
+        <v>12664689000</v>
       </c>
       <c r="AW3" t="n">
-        <v>9039797000</v>
+        <v>14018521000</v>
       </c>
       <c r="AX3" t="n">
-        <v>9039797000</v>
+        <v>14018521000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-214453680</v>
+        <v>-44525880</v>
       </c>
       <c r="C4" t="n">
         <v>0.21</v>
       </c>
       <c r="D4" t="n">
-        <v>-266901000</v>
+        <v>-333516000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1021208000</v>
+        <v>-212028000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1021208000</v>
+        <v>-212028000</v>
       </c>
       <c r="G4" t="n">
-        <v>-2588642000</v>
+        <v>-860793000</v>
       </c>
       <c r="H4" t="n">
-        <v>75067000</v>
+        <v>81488000</v>
       </c>
       <c r="I4" t="n">
-        <v>12664689000</v>
+        <v>7929178000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1288109000</v>
+        <v>-545544000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1363176000</v>
+        <v>-627032000</v>
       </c>
       <c r="L4" t="n">
-        <v>-369262000</v>
+        <v>-199857000</v>
       </c>
       <c r="M4" t="n">
-        <v>383248000</v>
+        <v>196286000</v>
       </c>
       <c r="N4" t="n">
-        <v>21904000</v>
+        <v>32242000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1781887680</v>
+        <v>-693290880</v>
       </c>
       <c r="P4" t="n">
-        <v>-2588642000</v>
+        <v>-860793000</v>
       </c>
       <c r="Q4" t="n">
-        <v>14241657000</v>
+        <v>9443752000</v>
       </c>
       <c r="R4" t="n">
-        <v>3573000</v>
+        <v>5660000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1087847000</v>
+        <v>-668420000</v>
       </c>
       <c r="T4" t="n">
-        <v>4545948000</v>
+        <v>4543175000</v>
       </c>
       <c r="U4" t="n">
-        <v>4545948000</v>
+        <v>4543175000</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.569</v>
+        <v>-0.189</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.569</v>
+        <v>-0.189</v>
       </c>
       <c r="X4" t="n">
-        <v>-2588642000</v>
+        <v>-860793000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2588642000</v>
+        <v>-860793000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2588642000</v>
+        <v>-860793000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-134890000</v>
+        <v>2526000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2453752000</v>
+        <v>-863319000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2453752000</v>
+        <v>-863319000</v>
       </c>
       <c r="AE4" t="n">
-        <v>707328000</v>
+        <v>40001000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1746424000</v>
+        <v>-823318000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-16293000</v>
+        <v>-6201000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1020925000</v>
+        <v>-212028000</v>
       </c>
       <c r="AI4" t="n">
-        <v>209070000</v>
+        <v>17713000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>479215000</v>
+        <v>194315000</v>
       </c>
       <c r="AK4" t="n">
-        <v>332640000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-369262000</v>
+        <v>-199857000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7918000</v>
+        <v>35813000</v>
       </c>
       <c r="AN4" t="n">
-        <v>383248000</v>
+        <v>196286000</v>
       </c>
       <c r="AO4" t="n">
-        <v>21904000</v>
+        <v>32242000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-223136000</v>
+        <v>-403955000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1576968000</v>
+        <v>1514574000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1588013000</v>
+        <v>1520014000</v>
       </c>
       <c r="AS4" t="n">
-        <v>694776000</v>
+        <v>547287000</v>
       </c>
       <c r="AT4" t="n">
-        <v>893237000</v>
+        <v>972727000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1353832000</v>
+        <v>1110619000</v>
       </c>
       <c r="AV4" t="n">
-        <v>12664689000</v>
+        <v>7929178000</v>
       </c>
       <c r="AW4" t="n">
-        <v>14018521000</v>
+        <v>9039797000</v>
       </c>
       <c r="AX4" t="n">
-        <v>14018521000</v>
+        <v>9039797000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-86072760</v>
+        <v>-21379003.04699</v>
       </c>
       <c r="C5" t="n">
-        <v>0.27</v>
+        <v>0.01231</v>
       </c>
       <c r="D5" t="n">
-        <v>124241000</v>
+        <v>391941000</v>
       </c>
       <c r="E5" t="n">
-        <v>-318788000</v>
+        <v>-1736719000</v>
       </c>
       <c r="F5" t="n">
-        <v>-318788000</v>
+        <v>-1736719000</v>
       </c>
       <c r="G5" t="n">
-        <v>-777504000</v>
+        <v>-1509333000</v>
       </c>
       <c r="H5" t="n">
-        <v>62823000</v>
+        <v>20144000</v>
       </c>
       <c r="I5" t="n">
-        <v>6406403000</v>
+        <v>1414125000</v>
       </c>
       <c r="J5" t="n">
-        <v>-194547000</v>
+        <v>-1344778000</v>
       </c>
       <c r="K5" t="n">
-        <v>-257370000</v>
+        <v>-1364922000</v>
       </c>
       <c r="L5" t="n">
-        <v>-163721000</v>
+        <v>-119155000</v>
       </c>
       <c r="M5" t="n">
-        <v>249540000</v>
+        <v>167410000</v>
       </c>
       <c r="N5" t="n">
-        <v>90222000</v>
+        <v>48255000</v>
       </c>
       <c r="O5" t="n">
-        <v>-544788760</v>
+        <v>206006996.95301</v>
       </c>
       <c r="P5" t="n">
-        <v>-777504000</v>
+        <v>-1509333000</v>
       </c>
       <c r="Q5" t="n">
-        <v>8143990000</v>
+        <v>1865299000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-369800000</v>
+        <v>-1826304000</v>
       </c>
       <c r="T5" t="n">
-        <v>4590548000</v>
+        <v>4613371000</v>
       </c>
       <c r="U5" t="n">
-        <v>4590548000</v>
+        <v>4613371000</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.169</v>
+        <v>-0.327</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.169</v>
+        <v>-0.327</v>
       </c>
       <c r="X5" t="n">
-        <v>-777504000</v>
+        <v>-1509333000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-777504000</v>
+        <v>-1509333000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-777504000</v>
+        <v>-1509333000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-81313000</v>
+        <v>4136000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-696191000</v>
+        <v>-1513469000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-696191000</v>
+        <v>-1513469000</v>
       </c>
       <c r="AE5" t="n">
-        <v>189281000</v>
+        <v>-18863000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-506910000</v>
+        <v>-1532332000</v>
       </c>
       <c r="AG5" t="n">
-        <v>16626000</v>
+        <v>5430000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-318788000</v>
+        <v>-1736719000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-17543000</v>
+        <v>1552766000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>275028000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>61303000</v>
-      </c>
+        <v>183953000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-163721000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>4403000</v>
-      </c>
+        <v>-119155000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>249540000</v>
+        <v>167410000</v>
       </c>
       <c r="AO5" t="n">
-        <v>90222000</v>
+        <v>48255000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-67920000</v>
+        <v>-139377000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1737587000</v>
+        <v>451174000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1768801000</v>
+        <v>456184000</v>
       </c>
       <c r="AS5" t="n">
-        <v>485646000</v>
+        <v>126017000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1283155000</v>
+        <v>330167000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1669667000</v>
+        <v>311797000</v>
       </c>
       <c r="AV5" t="n">
-        <v>6406403000</v>
+        <v>1414125000</v>
       </c>
       <c r="AW5" t="n">
-        <v>8076070000</v>
+        <v>1725922000</v>
       </c>
       <c r="AX5" t="n">
-        <v>8076070000</v>
+        <v>1725922000</v>
       </c>
     </row>
   </sheetData>
@@ -1658,62 +1658,62 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>11000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>4711307545</v>
+        <v>4722307000</v>
       </c>
       <c r="D2" t="n">
-        <v>4722307545</v>
+        <v>4722307000</v>
       </c>
       <c r="E2" t="n">
-        <v>3826890000</v>
+        <v>4458309000</v>
       </c>
       <c r="F2" t="n">
-        <v>4380738000</v>
+        <v>8583591000</v>
       </c>
       <c r="G2" t="n">
-        <v>-1499964000</v>
+        <v>3768579000</v>
       </c>
       <c r="H2" t="n">
-        <v>2879991000</v>
+        <v>12414126000</v>
       </c>
       <c r="I2" t="n">
-        <v>-4213391000</v>
+        <v>4873936000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1499964000</v>
+        <v>3768579000</v>
       </c>
       <c r="K2" t="n">
-        <v>783000</v>
+        <v>93972000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1499964000</v>
+        <v>3924507000</v>
       </c>
       <c r="M2" t="n">
-        <v>-22265000</v>
+        <v>8575124000</v>
       </c>
       <c r="N2" t="n">
-        <v>-1559186000</v>
+        <v>5581262000</v>
       </c>
       <c r="O2" t="n">
-        <v>-59222000</v>
+        <v>1656755000</v>
       </c>
       <c r="P2" t="n">
-        <v>-1499964000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>3924507000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>10692000</v>
+      </c>
       <c r="R2" t="n">
-        <v>14515000</v>
+        <v>17187000</v>
       </c>
       <c r="S2" t="n">
-        <v>-1767890000</v>
+        <v>3294596000</v>
       </c>
       <c r="T2" t="n">
-        <v>415193000</v>
+        <v>508781000</v>
       </c>
       <c r="U2" t="n">
         <v>38702000</v>
@@ -1722,206 +1722,216 @@
         <v>38702000</v>
       </c>
       <c r="W2" t="n">
-        <v>10882478000</v>
+        <v>22302091000</v>
       </c>
       <c r="X2" t="n">
-        <v>1612996000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>5218102000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>23106000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>50103000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>100046000</v>
       </c>
       <c r="AB2" t="n">
-        <v>4000000</v>
+        <v>150958000</v>
       </c>
       <c r="AC2" t="n">
-        <v>130778000</v>
+        <v>186855000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1478218000</v>
+        <v>4707034000</v>
       </c>
       <c r="AE2" t="n">
-        <v>519000</v>
+        <v>56417000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1477699000</v>
+        <v>4650617000</v>
       </c>
       <c r="AG2" t="n">
-        <v>9269482000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>17083989000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2692000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>2902520000</v>
+        <v>3876557000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>264000</v>
+        <v>37555000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2902256000</v>
+        <v>3839002000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6028281000</v>
+        <v>8981548000</v>
       </c>
       <c r="AM2" t="n">
-        <v>5766700000</v>
+        <v>7907505000</v>
       </c>
       <c r="AN2" t="n">
-        <v>13439000</v>
+        <v>204245000</v>
       </c>
       <c r="AO2" t="n">
-        <v>248142000</v>
+        <v>830278000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>39520000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9323292000</v>
+        <v>27883353000</v>
       </c>
       <c r="AR2" t="n">
-        <v>4267201000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>5925428000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>55580000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>281207000</v>
+        <v>709043000</v>
       </c>
       <c r="AU2" t="n">
-        <v>3679454000</v>
+        <v>3802138000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2081049000</v>
+        <v>2538674000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1598405000</v>
+        <v>1263464000</v>
       </c>
       <c r="AX2" t="n">
-        <v>66400000</v>
+        <v>687500000</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>155928000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>155928000</v>
       </c>
       <c r="BA2" t="n">
-        <v>240140000</v>
+        <v>290129000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-282388000</v>
+        <v>-186891000</v>
       </c>
       <c r="BC2" t="n">
-        <v>522528000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>18394000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>477020000</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
+        <v>290129000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>161622000</v>
+        <v>139699000</v>
       </c>
       <c r="BG2" t="n">
-        <v>342512000</v>
+        <v>337321000</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>5056091000</v>
+        <v>21957925000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>63142000</v>
+        <v>220985000</v>
       </c>
       <c r="BK2" t="n">
-        <v>704622000</v>
+        <v>1362982000</v>
       </c>
       <c r="BL2" t="n">
-        <v>2251325000</v>
+        <v>11913856000</v>
       </c>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
-        <v>2221006000</v>
+        <v>11881536000</v>
       </c>
       <c r="BO2" t="n">
-        <v>30319000</v>
+        <v>32320000</v>
       </c>
       <c r="BP2" t="n">
-        <v>1279908000</v>
+        <v>3938156000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>204029000</v>
+        <v>426889000</v>
       </c>
       <c r="BR2" t="n">
-        <v>-363889000</v>
+        <v>-254826000</v>
       </c>
       <c r="BS2" t="n">
-        <v>567918000</v>
+        <v>681715000</v>
       </c>
       <c r="BT2" t="n">
-        <v>553065000</v>
-      </c>
-      <c r="BU2" t="inlineStr"/>
+        <v>4095057000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>63747000</v>
+      </c>
       <c r="BV2" t="n">
-        <v>553065000</v>
+        <v>4031310000</v>
       </c>
       <c r="BW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>214106000</v>
+        <v>212374000</v>
       </c>
       <c r="C3" t="n">
-        <v>4508201545</v>
+        <v>4509933545</v>
       </c>
       <c r="D3" t="n">
         <v>4722307545</v>
       </c>
       <c r="E3" t="n">
-        <v>6742259000</v>
+        <v>6951135000</v>
       </c>
       <c r="F3" t="n">
-        <v>7830945000</v>
+        <v>8323962000</v>
       </c>
       <c r="G3" t="n">
-        <v>-497175000</v>
+        <v>238819000</v>
       </c>
       <c r="H3" t="n">
-        <v>7719393000</v>
+        <v>8920051000</v>
       </c>
       <c r="I3" t="n">
-        <v>2995395000</v>
+        <v>4345466000</v>
       </c>
       <c r="J3" t="n">
-        <v>-497175000</v>
+        <v>238819000</v>
       </c>
       <c r="K3" t="n">
-        <v>100525000</v>
+        <v>120771000</v>
       </c>
       <c r="L3" t="n">
-        <v>-11027000</v>
+        <v>716860000</v>
       </c>
       <c r="M3" t="n">
-        <v>5230888000</v>
+        <v>6553614000</v>
       </c>
       <c r="N3" t="n">
-        <v>2072284000</v>
+        <v>2693358000</v>
       </c>
       <c r="O3" t="n">
-        <v>2083311000</v>
+        <v>1976498000</v>
       </c>
       <c r="P3" t="n">
-        <v>-11027000</v>
+        <v>716860000</v>
       </c>
       <c r="Q3" t="n">
-        <v>11691000</v>
+        <v>6310000</v>
       </c>
       <c r="R3" t="n">
         <v>15804000</v>
       </c>
       <c r="S3" t="n">
-        <v>-235887000</v>
+        <v>688061000</v>
       </c>
       <c r="T3" t="n">
         <v>508781000</v>
@@ -1933,206 +1943,216 @@
         <v>38702000</v>
       </c>
       <c r="W3" t="n">
-        <v>17281301000</v>
+        <v>17293434000</v>
       </c>
       <c r="X3" t="n">
-        <v>5897000000</v>
+        <v>6460542000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>10272000</v>
+      </c>
       <c r="AA3" t="n">
-        <v>346662000</v>
+        <v>324946000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5000000</v>
+        <v>13443000</v>
       </c>
       <c r="AC3" t="n">
-        <v>190497000</v>
+        <v>191015000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5315794000</v>
+        <v>5920866000</v>
       </c>
       <c r="AE3" t="n">
-        <v>73879000</v>
+        <v>84112000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5241915000</v>
+        <v>5836754000</v>
       </c>
       <c r="AG3" t="n">
-        <v>11384301000</v>
+        <v>10832892000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>2515151000</v>
+        <v>2403096000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26646000</v>
+        <v>36659000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2488505000</v>
+        <v>2366437000</v>
       </c>
       <c r="AL3" t="n">
-        <v>8074752000</v>
+        <v>7749929000</v>
       </c>
       <c r="AM3" t="n">
-        <v>7195479000</v>
+        <v>6980764000</v>
       </c>
       <c r="AN3" t="n">
-        <v>13155000</v>
+        <v>12967000</v>
       </c>
       <c r="AO3" t="n">
-        <v>863605000</v>
+        <v>716638000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2513000</v>
+        <v>39560000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19353585000</v>
+        <v>19986792000</v>
       </c>
       <c r="AR3" t="n">
-        <v>4973889000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>4808434000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>34164000</v>
+      </c>
       <c r="AT3" t="n">
-        <v>409501000</v>
+        <v>283051000</v>
       </c>
       <c r="AU3" t="n">
-        <v>3389814000</v>
+        <v>3380945000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2315077000</v>
+        <v>2194260000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1074737000</v>
+        <v>1186685000</v>
       </c>
       <c r="AX3" t="n">
-        <v>321600000</v>
+        <v>332500000</v>
       </c>
       <c r="AY3" t="n">
-        <v>486148000</v>
+        <v>478041000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>486148000</v>
+        <v>478041000</v>
       </c>
       <c r="BA3" t="n">
-        <v>366826000</v>
+        <v>333897000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-268320000</v>
+        <v>-222405000</v>
       </c>
       <c r="BC3" t="n">
-        <v>635146000</v>
+        <v>556302000</v>
       </c>
       <c r="BD3" t="n">
-        <v>29603000</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>34164000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>299733000</v>
+      </c>
       <c r="BF3" t="n">
-        <v>180336000</v>
+        <v>154174000</v>
       </c>
       <c r="BG3" t="n">
-        <v>425207000</v>
+        <v>367964000</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>14379696000</v>
+        <v>15178358000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>456477000</v>
+        <v>494154000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1458214000</v>
+        <v>1486230000</v>
       </c>
       <c r="BL3" t="n">
-        <v>9731539000</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
+        <v>9688625000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>30059000</v>
+      </c>
       <c r="BN3" t="n">
-        <v>9701091000</v>
+        <v>9658566000</v>
       </c>
       <c r="BO3" t="n">
-        <v>30448000</v>
+        <v>30059000</v>
       </c>
       <c r="BP3" t="n">
-        <v>1479025000</v>
+        <v>1890019000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>266280000</v>
+        <v>367274000</v>
       </c>
       <c r="BR3" t="n">
-        <v>-377527000</v>
+        <v>-311611000</v>
       </c>
       <c r="BS3" t="n">
-        <v>643807000</v>
+        <v>678885000</v>
       </c>
       <c r="BT3" t="n">
-        <v>988161000</v>
+        <v>1252056000</v>
       </c>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="n">
-        <v>988161000</v>
-      </c>
-      <c r="BW3" t="inlineStr"/>
+        <v>1252056000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1252056000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>212374000</v>
+        <v>214106000</v>
       </c>
       <c r="C4" t="n">
-        <v>4509933545</v>
+        <v>4508201545</v>
       </c>
       <c r="D4" t="n">
         <v>4722307545</v>
       </c>
       <c r="E4" t="n">
-        <v>6951135000</v>
+        <v>6742259000</v>
       </c>
       <c r="F4" t="n">
-        <v>8323962000</v>
+        <v>7830945000</v>
       </c>
       <c r="G4" t="n">
-        <v>238819000</v>
+        <v>-497175000</v>
       </c>
       <c r="H4" t="n">
-        <v>8920051000</v>
+        <v>7719393000</v>
       </c>
       <c r="I4" t="n">
-        <v>4345466000</v>
+        <v>2995395000</v>
       </c>
       <c r="J4" t="n">
-        <v>238819000</v>
+        <v>-497175000</v>
       </c>
       <c r="K4" t="n">
-        <v>120771000</v>
+        <v>100525000</v>
       </c>
       <c r="L4" t="n">
-        <v>716860000</v>
+        <v>-11027000</v>
       </c>
       <c r="M4" t="n">
-        <v>6553614000</v>
+        <v>5230888000</v>
       </c>
       <c r="N4" t="n">
-        <v>2693358000</v>
+        <v>2072284000</v>
       </c>
       <c r="O4" t="n">
-        <v>1976498000</v>
+        <v>2083311000</v>
       </c>
       <c r="P4" t="n">
-        <v>716860000</v>
+        <v>-11027000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6310000</v>
+        <v>11691000</v>
       </c>
       <c r="R4" t="n">
         <v>15804000</v>
       </c>
       <c r="S4" t="n">
-        <v>688061000</v>
+        <v>-235887000</v>
       </c>
       <c r="T4" t="n">
         <v>508781000</v>
@@ -2144,217 +2164,207 @@
         <v>38702000</v>
       </c>
       <c r="W4" t="n">
-        <v>17293434000</v>
+        <v>17281301000</v>
       </c>
       <c r="X4" t="n">
-        <v>6460542000</v>
+        <v>5897000000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>10272000</v>
-      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>324946000</v>
+        <v>346662000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13443000</v>
+        <v>5000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>191015000</v>
+        <v>190497000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5920866000</v>
+        <v>5315794000</v>
       </c>
       <c r="AE4" t="n">
-        <v>84112000</v>
+        <v>73879000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5836754000</v>
+        <v>5241915000</v>
       </c>
       <c r="AG4" t="n">
-        <v>10832892000</v>
+        <v>11384301000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>2403096000</v>
+        <v>2515151000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36659000</v>
+        <v>26646000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2366437000</v>
+        <v>2488505000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7749929000</v>
+        <v>8074752000</v>
       </c>
       <c r="AM4" t="n">
-        <v>6980764000</v>
+        <v>7195479000</v>
       </c>
       <c r="AN4" t="n">
-        <v>12967000</v>
+        <v>13155000</v>
       </c>
       <c r="AO4" t="n">
-        <v>716638000</v>
+        <v>863605000</v>
       </c>
       <c r="AP4" t="n">
-        <v>39560000</v>
+        <v>2513000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19986792000</v>
+        <v>19353585000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4808434000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>34164000</v>
-      </c>
+        <v>4973889000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>283051000</v>
+        <v>409501000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3380945000</v>
+        <v>3389814000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2194260000</v>
+        <v>2315077000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1186685000</v>
+        <v>1074737000</v>
       </c>
       <c r="AX4" t="n">
-        <v>332500000</v>
+        <v>321600000</v>
       </c>
       <c r="AY4" t="n">
-        <v>478041000</v>
+        <v>486148000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>478041000</v>
+        <v>486148000</v>
       </c>
       <c r="BA4" t="n">
-        <v>333897000</v>
+        <v>366826000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-222405000</v>
+        <v>-268320000</v>
       </c>
       <c r="BC4" t="n">
-        <v>556302000</v>
+        <v>635146000</v>
       </c>
       <c r="BD4" t="n">
-        <v>34164000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>299733000</v>
-      </c>
+        <v>29603000</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>154174000</v>
+        <v>180336000</v>
       </c>
       <c r="BG4" t="n">
-        <v>367964000</v>
+        <v>425207000</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>15178358000</v>
+        <v>14379696000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>494154000</v>
+        <v>456477000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1486230000</v>
+        <v>1458214000</v>
       </c>
       <c r="BL4" t="n">
-        <v>9688625000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>30059000</v>
-      </c>
+        <v>9731539000</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>9658566000</v>
+        <v>9701091000</v>
       </c>
       <c r="BO4" t="n">
-        <v>30059000</v>
+        <v>30448000</v>
       </c>
       <c r="BP4" t="n">
-        <v>1890019000</v>
+        <v>1479025000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>367274000</v>
+        <v>266280000</v>
       </c>
       <c r="BR4" t="n">
-        <v>-311611000</v>
+        <v>-377527000</v>
       </c>
       <c r="BS4" t="n">
-        <v>678885000</v>
+        <v>643807000</v>
       </c>
       <c r="BT4" t="n">
-        <v>1252056000</v>
+        <v>988161000</v>
       </c>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="n">
-        <v>1252056000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1252056000</v>
-      </c>
+        <v>988161000</v>
+      </c>
+      <c r="BW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>11000000</v>
+      </c>
       <c r="C5" t="n">
-        <v>4722307000</v>
+        <v>4711307545</v>
       </c>
       <c r="D5" t="n">
-        <v>4722307000</v>
+        <v>4722307545</v>
       </c>
       <c r="E5" t="n">
-        <v>4458309000</v>
+        <v>3826890000</v>
       </c>
       <c r="F5" t="n">
-        <v>8583591000</v>
+        <v>4380738000</v>
       </c>
       <c r="G5" t="n">
-        <v>3768579000</v>
+        <v>-1499964000</v>
       </c>
       <c r="H5" t="n">
-        <v>12414126000</v>
+        <v>2879991000</v>
       </c>
       <c r="I5" t="n">
-        <v>4873936000</v>
+        <v>-4213391000</v>
       </c>
       <c r="J5" t="n">
-        <v>3768579000</v>
+        <v>-1499964000</v>
       </c>
       <c r="K5" t="n">
-        <v>93972000</v>
+        <v>783000</v>
       </c>
       <c r="L5" t="n">
-        <v>3924507000</v>
+        <v>-1499964000</v>
       </c>
       <c r="M5" t="n">
-        <v>8575124000</v>
+        <v>-22265000</v>
       </c>
       <c r="N5" t="n">
-        <v>5581262000</v>
+        <v>-1559186000</v>
       </c>
       <c r="O5" t="n">
-        <v>1656755000</v>
+        <v>-59222000</v>
       </c>
       <c r="P5" t="n">
-        <v>3924507000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>10692000</v>
-      </c>
+        <v>-1499964000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>17187000</v>
+        <v>14515000</v>
       </c>
       <c r="S5" t="n">
-        <v>3294596000</v>
+        <v>-1767890000</v>
       </c>
       <c r="T5" t="n">
-        <v>508781000</v>
+        <v>415193000</v>
       </c>
       <c r="U5" t="n">
         <v>38702000</v>
@@ -2363,156 +2373,146 @@
         <v>38702000</v>
       </c>
       <c r="W5" t="n">
-        <v>22302091000</v>
+        <v>10882478000</v>
       </c>
       <c r="X5" t="n">
-        <v>5218102000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>23106000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>50103000</v>
-      </c>
+        <v>1612996000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>100046000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>150958000</v>
+        <v>4000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>186855000</v>
+        <v>130778000</v>
       </c>
       <c r="AD5" t="n">
-        <v>4707034000</v>
+        <v>1478218000</v>
       </c>
       <c r="AE5" t="n">
-        <v>56417000</v>
+        <v>519000</v>
       </c>
       <c r="AF5" t="n">
-        <v>4650617000</v>
+        <v>1477699000</v>
       </c>
       <c r="AG5" t="n">
-        <v>17083989000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2692000</v>
-      </c>
+        <v>9269482000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>3876557000</v>
+        <v>2902520000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>37555000</v>
+        <v>264000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3839002000</v>
+        <v>2902256000</v>
       </c>
       <c r="AL5" t="n">
-        <v>8981548000</v>
+        <v>6028281000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7907505000</v>
+        <v>5766700000</v>
       </c>
       <c r="AN5" t="n">
-        <v>204245000</v>
+        <v>13439000</v>
       </c>
       <c r="AO5" t="n">
-        <v>830278000</v>
+        <v>248142000</v>
       </c>
       <c r="AP5" t="n">
-        <v>39520000</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27883353000</v>
+        <v>9323292000</v>
       </c>
       <c r="AR5" t="n">
-        <v>5925428000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>55580000</v>
-      </c>
+        <v>4267201000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>709043000</v>
+        <v>281207000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3802138000</v>
+        <v>3679454000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2538674000</v>
+        <v>2081049000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1263464000</v>
+        <v>1598405000</v>
       </c>
       <c r="AX5" t="n">
-        <v>687500000</v>
+        <v>66400000</v>
       </c>
       <c r="AY5" t="n">
-        <v>155928000</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>155928000</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>290129000</v>
+        <v>240140000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-186891000</v>
+        <v>-282388000</v>
       </c>
       <c r="BC5" t="n">
-        <v>477020000</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
-        <v>290129000</v>
-      </c>
+        <v>522528000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>18394000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>139699000</v>
+        <v>161622000</v>
       </c>
       <c r="BG5" t="n">
-        <v>337321000</v>
+        <v>342512000</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>21957925000</v>
+        <v>5056091000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>220985000</v>
+        <v>63142000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1362982000</v>
+        <v>704622000</v>
       </c>
       <c r="BL5" t="n">
-        <v>11913856000</v>
+        <v>2251325000</v>
       </c>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>11881536000</v>
+        <v>2221006000</v>
       </c>
       <c r="BO5" t="n">
-        <v>32320000</v>
+        <v>30319000</v>
       </c>
       <c r="BP5" t="n">
-        <v>3938156000</v>
+        <v>1279908000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>426889000</v>
+        <v>204029000</v>
       </c>
       <c r="BR5" t="n">
-        <v>-254826000</v>
+        <v>-363889000</v>
       </c>
       <c r="BS5" t="n">
-        <v>681715000</v>
+        <v>567918000</v>
       </c>
       <c r="BT5" t="n">
-        <v>4095057000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>63747000</v>
-      </c>
+        <v>553065000</v>
+      </c>
+      <c r="BU5" t="inlineStr"/>
       <c r="BV5" t="n">
-        <v>4031310000</v>
+        <v>553065000</v>
       </c>
       <c r="BW5" t="inlineStr"/>
     </row>
@@ -2794,622 +2794,622 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-988837000</v>
+        <v>-3216575000</v>
       </c>
       <c r="C2" t="n">
-        <v>-39728000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-982090000</v>
+        <v>-4116744000</v>
       </c>
       <c r="E2" t="n">
-        <v>758363000</v>
+        <v>6061404000</v>
       </c>
       <c r="F2" t="n">
-        <v>1440000</v>
+        <v>-31078000</v>
       </c>
       <c r="G2" t="n">
-        <v>-8612000</v>
+        <v>-22668000</v>
       </c>
       <c r="H2" t="n">
-        <v>553065000</v>
+        <v>4031310000</v>
       </c>
       <c r="I2" t="n">
-        <v>988161000</v>
+        <v>5131678000</v>
       </c>
       <c r="J2" t="n">
-        <v>165749000</v>
+        <v>-47768000</v>
       </c>
       <c r="K2" t="n">
-        <v>-600845000</v>
+        <v>-1052600000</v>
       </c>
       <c r="L2" t="n">
-        <v>-338557000</v>
+        <v>1505018000</v>
       </c>
       <c r="M2" t="n">
-        <v>-70601000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>-291879000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-68208000</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-38288000</v>
+        <v>-31078000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-39728000</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1440000</v>
+        <v>-31078000</v>
       </c>
       <c r="S2" t="n">
-        <v>-223727000</v>
+        <v>1944660000</v>
       </c>
       <c r="T2" t="n">
-        <v>-223727000</v>
+        <v>1944660000</v>
       </c>
       <c r="U2" t="n">
-        <v>-982090000</v>
+        <v>-4116744000</v>
       </c>
       <c r="V2" t="n">
-        <v>758363000</v>
+        <v>6061404000</v>
       </c>
       <c r="W2" t="n">
-        <v>717937000</v>
+        <v>636289000</v>
       </c>
       <c r="X2" t="n">
-        <v>3000</v>
+        <v>167617000</v>
       </c>
       <c r="Y2" t="n">
-        <v>203703000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>32200000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>32200000</v>
-      </c>
+        <v>469449000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-63747000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-63747000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>262614000</v>
+        <v>-412961000</v>
       </c>
       <c r="AF2" t="n">
-        <v>659362000</v>
+        <v>7000000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-396748000</v>
+        <v>-419961000</v>
       </c>
       <c r="AH2" t="n">
-        <v>96640000</v>
+        <v>-22317000</v>
       </c>
       <c r="AI2" t="n">
-        <v>105252000</v>
+        <v>351000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-8612000</v>
+        <v>-22668000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-980225000</v>
+        <v>-3193907000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-50138000</v>
+        <v>-529559000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-133082000</v>
+        <v>-505312000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-714655000</v>
+        <v>-2481712000</v>
       </c>
       <c r="AO2" t="n">
-        <v>79675000</v>
+        <v>-295318000</v>
       </c>
       <c r="AP2" t="n">
-        <v>186012000</v>
+        <v>-1727436000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-998453000</v>
+        <v>-1163779000</v>
       </c>
       <c r="AR2" t="n">
-        <v>18111000</v>
+        <v>704821000</v>
       </c>
       <c r="AS2" t="n">
-        <v>106315000</v>
+        <v>558775000</v>
       </c>
       <c r="AT2" t="n">
-        <v>9895000</v>
+        <v>33305000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-28057000</v>
+        <v>67192000</v>
       </c>
       <c r="AV2" t="n">
-        <v>20144000</v>
+        <v>62823000</v>
       </c>
       <c r="AW2" t="n">
-        <v>20144000</v>
+        <v>62823000</v>
       </c>
       <c r="AX2" t="n">
-        <v>6523000</v>
+        <v>5632000</v>
       </c>
       <c r="AY2" t="n">
-        <v>24095000</v>
+        <v>41852000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1528670000</v>
+        <v>31167000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-1532331000</v>
+        <v>-2665946000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-379918000</v>
+        <v>-493420000</v>
       </c>
       <c r="C3" t="n">
-        <v>-220325000</v>
+        <v>-68438000</v>
       </c>
       <c r="D3" t="n">
-        <v>-4222373000</v>
+        <v>-3500470000</v>
       </c>
       <c r="E3" t="n">
-        <v>4042584000</v>
+        <v>2342525000</v>
       </c>
       <c r="F3" t="n">
-        <v>-209000</v>
+        <v>-65754000</v>
       </c>
       <c r="G3" t="n">
-        <v>-63608000</v>
+        <v>-8505000</v>
       </c>
       <c r="H3" t="n">
-        <v>988161000</v>
+        <v>1252056000</v>
       </c>
       <c r="I3" t="n">
-        <v>1252056000</v>
+        <v>4031310000</v>
       </c>
       <c r="J3" t="n">
-        <v>-15849000</v>
+        <v>174774000</v>
       </c>
       <c r="K3" t="n">
-        <v>-248046000</v>
+        <v>-2954028000</v>
       </c>
       <c r="L3" t="n">
-        <v>-191171000</v>
+        <v>-1388505000</v>
       </c>
       <c r="M3" t="n">
-        <v>237226000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>140420000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-200000000</v>
+      </c>
       <c r="O3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-134192000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-68438000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-65754000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-1157945000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1157945000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-3500470000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2342525000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1080608000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>66158000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14007000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>67321000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>67321000</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>-220534000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-220325000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-209000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-179789000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-179789000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-4222373000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4042584000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>259435000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>199000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>23852000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>5492000</v>
+        <v>-1412454000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8042000</v>
+        <v>257733000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2550000</v>
+        <v>-1670187000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-32346000</v>
+        <v>-8084000</v>
       </c>
       <c r="AI3" t="n">
-        <v>31262000</v>
+        <v>421000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-63608000</v>
+        <v>-8505000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-316310000</v>
+        <v>-484915000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-107037000</v>
+        <v>-266815000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-730838000</v>
+        <v>-516363000</v>
       </c>
       <c r="AN3" t="n">
-        <v>636698000</v>
+        <v>-562277000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-41333000</v>
+        <v>-3878686000</v>
       </c>
       <c r="AP3" t="n">
-        <v>122827000</v>
+        <v>-166767000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>436388000</v>
+        <v>4165785000</v>
       </c>
       <c r="AR3" t="n">
-        <v>118816000</v>
+        <v>-682609000</v>
       </c>
       <c r="AS3" t="n">
-        <v>218854000</v>
+        <v>772025000</v>
       </c>
       <c r="AT3" t="n">
-        <v>30065000</v>
+        <v>31393000</v>
       </c>
       <c r="AU3" t="n">
-        <v>185889000</v>
+        <v>765369000</v>
       </c>
       <c r="AV3" t="n">
-        <v>81488000</v>
+        <v>75067000</v>
       </c>
       <c r="AW3" t="n">
-        <v>81488000</v>
+        <v>75067000</v>
       </c>
       <c r="AX3" t="n">
-        <v>29979000</v>
+        <v>60110000</v>
       </c>
       <c r="AY3" t="n">
-        <v>4839000</v>
+        <v>113000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22183000</v>
+        <v>143683000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-823318000</v>
+        <v>-1746424000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-493420000</v>
+        <v>-379918000</v>
       </c>
       <c r="C4" t="n">
-        <v>-68438000</v>
+        <v>-220325000</v>
       </c>
       <c r="D4" t="n">
-        <v>-3500470000</v>
+        <v>-4222373000</v>
       </c>
       <c r="E4" t="n">
-        <v>2342525000</v>
+        <v>4042584000</v>
       </c>
       <c r="F4" t="n">
-        <v>-65754000</v>
+        <v>-209000</v>
       </c>
       <c r="G4" t="n">
-        <v>-8505000</v>
+        <v>-63608000</v>
       </c>
       <c r="H4" t="n">
+        <v>988161000</v>
+      </c>
+      <c r="I4" t="n">
         <v>1252056000</v>
       </c>
-      <c r="I4" t="n">
-        <v>4031310000</v>
-      </c>
       <c r="J4" t="n">
-        <v>174774000</v>
+        <v>-15849000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2954028000</v>
+        <v>-248046000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1388505000</v>
+        <v>-191171000</v>
       </c>
       <c r="M4" t="n">
-        <v>140420000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-200000000</v>
-      </c>
+        <v>237226000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-200000000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-134192000</v>
+        <v>-220534000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-68438000</v>
+        <v>-220325000</v>
       </c>
       <c r="R4" t="n">
-        <v>-65754000</v>
+        <v>-209000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1157945000</v>
+        <v>-179789000</v>
       </c>
       <c r="T4" t="n">
-        <v>-1157945000</v>
+        <v>-179789000</v>
       </c>
       <c r="U4" t="n">
-        <v>-3500470000</v>
+        <v>-4222373000</v>
       </c>
       <c r="V4" t="n">
-        <v>2342525000</v>
+        <v>4042584000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1080608000</v>
+        <v>259435000</v>
       </c>
       <c r="X4" t="n">
-        <v>66158000</v>
+        <v>199000</v>
       </c>
       <c r="Y4" t="n">
-        <v>14007000</v>
+        <v>23852000</v>
       </c>
       <c r="Z4" t="n">
-        <v>67321000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>67321000</v>
-      </c>
-      <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
       <c r="AE4" t="n">
-        <v>-1412454000</v>
+        <v>5492000</v>
       </c>
       <c r="AF4" t="n">
-        <v>257733000</v>
+        <v>8042000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1670187000</v>
+        <v>-2550000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-8084000</v>
+        <v>-32346000</v>
       </c>
       <c r="AI4" t="n">
-        <v>421000</v>
+        <v>31262000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-8505000</v>
+        <v>-63608000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-484915000</v>
+        <v>-316310000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-266815000</v>
+        <v>-107037000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-516363000</v>
+        <v>-730838000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-562277000</v>
+        <v>636698000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-3878686000</v>
+        <v>-41333000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-166767000</v>
+        <v>122827000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4165785000</v>
+        <v>436388000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-682609000</v>
+        <v>118816000</v>
       </c>
       <c r="AS4" t="n">
-        <v>772025000</v>
+        <v>218854000</v>
       </c>
       <c r="AT4" t="n">
-        <v>31393000</v>
+        <v>30065000</v>
       </c>
       <c r="AU4" t="n">
-        <v>765369000</v>
+        <v>185889000</v>
       </c>
       <c r="AV4" t="n">
-        <v>75067000</v>
+        <v>81488000</v>
       </c>
       <c r="AW4" t="n">
-        <v>75067000</v>
+        <v>81488000</v>
       </c>
       <c r="AX4" t="n">
-        <v>60110000</v>
+        <v>29979000</v>
       </c>
       <c r="AY4" t="n">
-        <v>113000</v>
+        <v>4839000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>143683000</v>
+        <v>22183000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1746424000</v>
+        <v>-823318000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-3216575000</v>
+        <v>-988837000</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-39728000</v>
       </c>
       <c r="D5" t="n">
-        <v>-4116744000</v>
+        <v>-982090000</v>
       </c>
       <c r="E5" t="n">
-        <v>6061404000</v>
+        <v>758363000</v>
       </c>
       <c r="F5" t="n">
-        <v>-31078000</v>
+        <v>1440000</v>
       </c>
       <c r="G5" t="n">
-        <v>-22668000</v>
+        <v>-8612000</v>
       </c>
       <c r="H5" t="n">
-        <v>4031310000</v>
+        <v>553065000</v>
       </c>
       <c r="I5" t="n">
-        <v>5131678000</v>
+        <v>988161000</v>
       </c>
       <c r="J5" t="n">
-        <v>-47768000</v>
+        <v>165749000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1052600000</v>
+        <v>-600845000</v>
       </c>
       <c r="L5" t="n">
-        <v>1505018000</v>
+        <v>-338557000</v>
       </c>
       <c r="M5" t="n">
-        <v>-291879000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-68208000</v>
-      </c>
+        <v>-70601000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-31078000</v>
+        <v>-38288000</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-39728000</v>
       </c>
       <c r="R5" t="n">
-        <v>-31078000</v>
+        <v>1440000</v>
       </c>
       <c r="S5" t="n">
-        <v>1944660000</v>
+        <v>-223727000</v>
       </c>
       <c r="T5" t="n">
-        <v>1944660000</v>
+        <v>-223727000</v>
       </c>
       <c r="U5" t="n">
-        <v>-4116744000</v>
+        <v>-982090000</v>
       </c>
       <c r="V5" t="n">
-        <v>6061404000</v>
+        <v>758363000</v>
       </c>
       <c r="W5" t="n">
-        <v>636289000</v>
+        <v>717937000</v>
       </c>
       <c r="X5" t="n">
-        <v>167617000</v>
+        <v>3000</v>
       </c>
       <c r="Y5" t="n">
-        <v>469449000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-63747000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-63747000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>203703000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>32200000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>32200000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-412961000</v>
+        <v>262614000</v>
       </c>
       <c r="AF5" t="n">
-        <v>7000000</v>
+        <v>659362000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-419961000</v>
+        <v>-396748000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-22317000</v>
+        <v>96640000</v>
       </c>
       <c r="AI5" t="n">
-        <v>351000</v>
+        <v>105252000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-22668000</v>
+        <v>-8612000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3193907000</v>
+        <v>-980225000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-529559000</v>
+        <v>-50138000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-505312000</v>
+        <v>-133082000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-2481712000</v>
+        <v>-714655000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-295318000</v>
+        <v>79675000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1727436000</v>
+        <v>186012000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1163779000</v>
+        <v>-998453000</v>
       </c>
       <c r="AR5" t="n">
-        <v>704821000</v>
+        <v>18111000</v>
       </c>
       <c r="AS5" t="n">
-        <v>558775000</v>
+        <v>106315000</v>
       </c>
       <c r="AT5" t="n">
-        <v>33305000</v>
+        <v>9895000</v>
       </c>
       <c r="AU5" t="n">
-        <v>67192000</v>
+        <v>-28057000</v>
       </c>
       <c r="AV5" t="n">
-        <v>62823000</v>
+        <v>20144000</v>
       </c>
       <c r="AW5" t="n">
-        <v>62823000</v>
+        <v>20144000</v>
       </c>
       <c r="AX5" t="n">
-        <v>5632000</v>
+        <v>6523000</v>
       </c>
       <c r="AY5" t="n">
-        <v>41852000</v>
+        <v>24095000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>31167000</v>
+        <v>1528670000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-2665946000</v>
+        <v>-1532331000</v>
       </c>
     </row>
   </sheetData>
@@ -3954,207 +3954,207 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EQ1" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Zheng  Huang', 'age': 42, 'title': 'Chief Executive Officer', 'yearBorn': 1983, 'fiscalYear': 2024, 'totalPay': 1511375, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chenlong  Zhang', 'age': 47, 'title': 'Executive Chairman', 'yearBorn': 1978, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Ho', 'age': 43, 'title': 'VP &amp; CEO of United States', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Zheng  Huang', 'age': 42, 'title': 'Chief Executive Officer', 'yearBorn': 1983, 'fiscalYear': 2024, 'totalPay': 1510561, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chenlong  Zhang', 'age': 47, 'title': 'Executive Chairman', 'yearBorn': 1978, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Ho', 'age': 43, 'title': 'VP &amp; CEO of United States', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4285,7 +4285,7 @@
         <v>7.98</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.227</v>
+        <v>-0.239</v>
       </c>
       <c r="AF2" t="n">
         <v>0.02923077</v>
@@ -4342,7 +4342,7 @@
         <v>0.019</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01909</v>
+        <v>0.019</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4380,7 +4380,7 @@
         <v>4711307545</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.36828908</v>
+        <v>-0.36809078</v>
       </c>
       <c r="BK2" t="n">
         <v>1735603200</v>
@@ -4418,10 +4418,10 @@
         <v>-20.818</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.46153843</v>
+        <v>0.3571428</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.03</v>
@@ -4531,70 +4531,72 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="b">
+      <c r="DB2" t="n">
         <v>0</v>
       </c>
-      <c r="DC2" t="n">
-        <v>1127957400000</v>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.018 - 0.02</t>
+        </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>1756454890</v>
-      </c>
-      <c r="DF2" t="n">
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>LANDSEA MGMT</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Landsea Green Management Limited</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>0.018 - 0.02</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
+      <c r="DH2" t="n">
+        <v>0.005999999</v>
       </c>
       <c r="DI2" t="n">
+        <v>0.46153837</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.013 - 0.028</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.0090000015</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.32142863</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>35.71428</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1743173169</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1743173169</v>
+      </c>
+      <c r="DP2" t="b">
         <v>0</v>
       </c>
-      <c r="DJ2" t="n">
-        <v>0.005999999</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.46153837</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>0.013 - 0.028</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.0090000015</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.32142863</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>46.153843</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1743173169</v>
-      </c>
       <c r="DQ2" t="n">
-        <v>1743173169</v>
-      </c>
-      <c r="DR2" t="b">
+        <v>-0.38</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DS2" t="n">
         <v>0</v>
       </c>
-      <c r="DS2" t="n">
-        <v>-0.38</v>
-      </c>
       <c r="DT2" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
@@ -4603,34 +4605,34 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-9.000115e-05</v>
+        <v>-0.0516177</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.0047145705</v>
+        <v>15</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0.051589906</v>
-      </c>
-      <c r="DZ2" t="n">
         <v>15</v>
       </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>Landsea Green Properties Co., Ltd.</t>
         </is>
       </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1756454890</v>
       </c>
       <c r="EE2" t="n">
         <v>0</v>
@@ -4640,47 +4642,45 @@
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>LANDSEA MGMT</t>
+          <t>PREPRE</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>Landsea Green Management Limited</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>finmb_4497166</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>finmb_4497166</t>
+          <t>Asia/Hong_Kong</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="EM2" t="n">
+      <c r="EL2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EN2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
+      </c>
+      <c r="EN2" t="b">
+        <v>0</v>
       </c>
       <c r="EO2" t="b">
         <v>0</v>
       </c>
-      <c r="EP2" t="b">
-        <v>0</v>
+      <c r="EP2" t="n">
+        <v>1127957400000</v>
       </c>
       <c r="EQ2" t="inlineStr"/>
     </row>
